--- a/Documentation/Week 4/Booked Hours/Booked_Hours_Lithasa.xlsx
+++ b/Documentation/Week 4/Booked Hours/Booked_Hours_Lithasa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 2/Booked Hours/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 4/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="65" documentId="8_{102A6B7F-044D-4847-8C31-4EB523215BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6810E97E-AF8C-406D-BDDC-23E5A138F47A}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Verdana"/>
@@ -345,14 +345,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -371,6 +363,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -789,55 +789,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1"/>
-    <col min="9" max="9" width="10.625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.625" style="1"/>
+    <col min="1" max="1" width="5.90625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.36328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6328125" style="1"/>
+    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
-    </row>
-    <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1">
+    <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="11"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="17" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.15" customHeight="1">
+    <row r="3" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="2" t="s">
         <v>7</v>
@@ -853,9 +853,9 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="16"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="H3" s="14"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -887,7 +887,7 @@
         <v>0.99999999994179234</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -919,7 +919,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -951,7 +951,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -983,7 +983,7 @@
         <v>0.99999999994179234</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>4</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>4</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>0.99999999994179234</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>4</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>1.7499999999417923</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>4</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>0.99999999994179234</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>4</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
       <c r="D14" s="4"/>
@@ -1193,7 +1193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
       <c r="D15" s="4"/>
@@ -1211,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="4"/>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="4"/>
@@ -1247,7 +1247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
       <c r="D18" s="4"/>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
       <c r="D19" s="4"/>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="C20" s="5"/>
       <c r="D20" s="4"/>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B21" s="4"/>
       <c r="C21" s="5"/>
       <c r="D21" s="4"/>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B22" s="4"/>
       <c r="C22" s="5"/>
       <c r="D22" s="4"/>
@@ -1337,7 +1337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B23" s="4"/>
       <c r="C23" s="5"/>
       <c r="D23" s="4"/>
@@ -1355,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
       <c r="D24" s="4"/>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
       <c r="D25" s="4"/>
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
       <c r="D26" s="4"/>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
       <c r="D27" s="4"/>
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
       <c r="D28" s="4"/>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
       <c r="D29" s="4"/>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
       <c r="D30" s="4"/>
@@ -1481,18 +1481,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="10" t="s">
+      <c r="C31" s="16"/>
+      <c r="D31" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="7" t="s">
         <v>4</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="2" t="s">
         <v>7</v>
@@ -1529,7 +1529,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="2:9">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
       <c r="D33" s="4"/>
@@ -1547,7 +1547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:9">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
       <c r="D34" s="4"/>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:9">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
       <c r="D35" s="4"/>
@@ -1583,7 +1583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:9">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="4"/>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:9">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
       <c r="D37" s="4"/>
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:9">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
       <c r="D38" s="4"/>
@@ -1637,7 +1637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:9">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
       <c r="D39" s="4"/>
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:9">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
       <c r="D40" s="4"/>
@@ -1673,7 +1673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:9">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
       <c r="D41" s="4"/>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:9">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B42" s="4"/>
       <c r="C42" s="5"/>
       <c r="D42" s="4"/>
@@ -1709,7 +1709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:9">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B43" s="4"/>
       <c r="C43" s="5"/>
       <c r="D43" s="4"/>
@@ -1727,7 +1727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:9">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
       <c r="D44" s="4"/>
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:9">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B45" s="4"/>
       <c r="C45" s="5"/>
       <c r="D45" s="4"/>
@@ -1763,7 +1763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:9">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
       <c r="D46" s="4"/>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:9">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B47" s="4"/>
       <c r="C47" s="5"/>
       <c r="D47" s="4"/>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:9">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48" s="4"/>
       <c r="C48" s="5"/>
       <c r="D48" s="4"/>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:9">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B49" s="4"/>
       <c r="C49" s="5"/>
       <c r="D49" s="4"/>
@@ -1835,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:9">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B50" s="4"/>
       <c r="C50" s="5"/>
       <c r="D50" s="4"/>
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:9">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51" s="4"/>
       <c r="C51" s="5"/>
       <c r="D51" s="4"/>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:9">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="4"/>
       <c r="C52" s="5"/>
       <c r="D52" s="4"/>
@@ -1889,7 +1889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:9">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53" s="4"/>
       <c r="C53" s="5"/>
       <c r="D53" s="4"/>
@@ -1907,7 +1907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:9">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54" s="4"/>
       <c r="C54" s="5"/>
       <c r="D54" s="4"/>
@@ -1925,7 +1925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:9">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B55" s="4"/>
       <c r="C55" s="5"/>
       <c r="D55" s="4"/>
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:9">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B56" s="4"/>
       <c r="C56" s="5"/>
       <c r="D56" s="4"/>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:9">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B57" s="4"/>
       <c r="C57" s="5"/>
       <c r="D57" s="4"/>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:9">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58" s="4"/>
       <c r="C58" s="5"/>
       <c r="D58" s="4"/>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:9">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59" s="4"/>
       <c r="C59" s="5"/>
       <c r="D59" s="4"/>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:9">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60" s="4"/>
       <c r="G60" s="6" t="str">
         <f t="shared" si="3"/>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:9">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B61" s="4"/>
       <c r="G61" s="6" t="str">
         <f t="shared" si="3"/>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:9">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B62" s="4"/>
       <c r="G62" s="6" t="str">
         <f t="shared" si="3"/>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:9">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B63" s="4"/>
       <c r="G63" s="6" t="str">
         <f t="shared" si="3"/>
@@ -2075,7 +2075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:9">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B64" s="4"/>
       <c r="G64" s="6" t="str">
         <f t="shared" si="3"/>
@@ -2090,18 +2090,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15">
+    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="10" t="s">
+      <c r="C65" s="16"/>
+      <c r="D65" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E65" s="11"/>
+      <c r="E65" s="16"/>
       <c r="F65" s="7" t="s">
         <v>4</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15">
+    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="9"/>
       <c r="B66" s="2" t="s">
         <v>7</v>
@@ -2138,7 +2138,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G67" s="6" t="str">
         <f t="shared" ref="G67:G98" si="5">IF(I67&gt;0,I67,IF(I67=0, " ", "ERROR"))</f>
         <v xml:space="preserve"> </v>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G68" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2166,7 +2166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G69" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G70" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G71" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G72" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G73" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2236,7 +2236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G74" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G75" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G76" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2278,7 +2278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G77" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G78" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2306,7 +2306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G79" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2320,7 +2320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G80" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2334,7 +2334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="7:9">
+    <row r="81" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G81" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2348,7 +2348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="7:9">
+    <row r="82" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G82" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2362,7 +2362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="7:9">
+    <row r="83" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G83" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2376,7 +2376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="7:9">
+    <row r="84" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G84" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="7:9">
+    <row r="85" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G85" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2404,7 +2404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="7:9">
+    <row r="86" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G86" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="7:9">
+    <row r="87" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G87" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="7:9">
+    <row r="88" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G88" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="7:9">
+    <row r="89" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G89" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2460,7 +2460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="7:9">
+    <row r="90" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G90" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2474,7 +2474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="7:9">
+    <row r="91" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G91" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="7:9">
+    <row r="92" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G92" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2502,7 +2502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="7:9">
+    <row r="93" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G93" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2516,7 +2516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="7:9">
+    <row r="94" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G94" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="7:9">
+    <row r="95" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G95" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="7:9">
+    <row r="96" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G96" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G97" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2572,7 +2572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G98" s="6" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
@@ -2586,18 +2586,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15">
+    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C99" s="11"/>
-      <c r="D99" s="10" t="s">
+      <c r="C99" s="16"/>
+      <c r="D99" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E99" s="11"/>
+      <c r="E99" s="16"/>
       <c r="F99" s="7" t="s">
         <v>4</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15">
+    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="9"/>
       <c r="B100" s="2" t="s">
         <v>7</v>
@@ -2634,7 +2634,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G101" s="6" t="str">
         <f t="shared" ref="G101:G132" si="8">IF(I101&gt;0,I101,IF(I101=0, " ", "ERROR"))</f>
         <v xml:space="preserve"> </v>
@@ -2648,7 +2648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G102" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2662,7 +2662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G103" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2676,7 +2676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G104" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G105" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2704,7 +2704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G106" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2718,7 +2718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G107" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2732,7 +2732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G108" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2746,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G109" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2760,7 +2760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G110" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2774,7 +2774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G111" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G112" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="7:9">
+    <row r="113" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G113" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2816,7 +2816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="7:9">
+    <row r="114" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G114" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2830,7 +2830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="7:9">
+    <row r="115" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G115" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="7:9">
+    <row r="116" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G116" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="7:9">
+    <row r="117" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G117" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2872,7 +2872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="7:9">
+    <row r="118" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G118" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2886,7 +2886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="7:9">
+    <row r="119" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G119" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2900,7 +2900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="7:9">
+    <row r="120" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G120" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="7:9">
+    <row r="121" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G121" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="7:9">
+    <row r="122" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G122" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2942,7 +2942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="7:9">
+    <row r="123" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G123" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2956,7 +2956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="7:9">
+    <row r="124" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G124" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2970,7 +2970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="7:9">
+    <row r="125" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G125" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2984,7 +2984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="7:9">
+    <row r="126" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G126" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -2998,7 +2998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="7:9">
+    <row r="127" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G127" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -3012,7 +3012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="7:9">
+    <row r="128" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G128" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -3026,7 +3026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="7:9">
+    <row r="129" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G129" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="7:9">
+    <row r="130" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G130" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="7:9">
+    <row r="131" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G131" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -3068,7 +3068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="7:9">
+    <row r="132" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G132" s="6" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve"> </v>
@@ -3084,6 +3084,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3097,18 +3109,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -3120,7 +3120,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3132,7 +3132,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
